--- a/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
+++ b/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us-analysis\InputData\elec\SoCtMbCtbDP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\Mexico\Models\eps-mexico\InputData\elec\SoCtMbCtbDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C2FD9E-EFCC-4DF9-82F0-7BE08C7CAA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E13260-0CA4-4BF3-B361-42BD0E7A7A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="10635" yWindow="2055" windowWidth="24510" windowHeight="17910" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -586,7 +586,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -610,7 +610,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -626,7 +626,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -634,7 +634,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -666,7 +666,7 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -682,7 +682,7 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -690,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
